--- a/public/data/contract_notes.xlsx
+++ b/public/data/contract_notes.xlsx
@@ -418,172 +418,172 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>9ce85069-9379-47dc-8fec-51a1b98e71ed</v>
+        <v>98c42733-9897-464d-bbd6-9f2d45f790c2</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D2" t="str">
-        <v>8804be40-aa6d-4db8-8332-6c0383240a8d</v>
+        <v>c0f92e8a-aa8b-4aa2-bec2-95cb55998bf6</v>
       </c>
       <c r="E2" t="str">
-        <v>&lt;h2&gt;Waldorf Astoria Transfer Contract&lt;/h2&gt;&lt;p&gt;Premium seaplane transfer service for Waldorf Astoria Maldives Ithaafushi guests. &lt;strong&gt;Key highlights:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;VIP lounge access included for suite guests&lt;/li&gt;&lt;li&gt;Dedicated check-in counter at TMA terminal&lt;/li&gt;&lt;li&gt;Priority boarding during peak season&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Contact: Reservations team at +960 400-0000&lt;/p&gt;</v>
+        <v>&lt;h2&gt;Waldorf Astoria Transfer &amp; Charter&lt;/h2&gt;&lt;p&gt;Dual contract covering both scheduled seaplane transfers and dedicated charter service for Waldorf Astoria Maldives Ithaafushi. &lt;strong&gt;Key highlights:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Transfer (CTR-001-001): VIP lounge access included for suite guests, dedicated check-in at TMA terminal&lt;/li&gt;&lt;li&gt;Charter (CTR-001-002): Private aircraft for large group bookings, aerial photography add-on available&lt;/li&gt;&lt;li&gt;Priority boarding during peak season Nov-Apr&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Contact: Marriott Reservations at +960 400-0000&lt;/p&gt;&lt;p&gt;&lt;em&gt;Transfer sub-contract expiring March 2026 - renewal talks initiated.&lt;/em&gt;&lt;/p&gt;</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>416b075c-7fed-4a0e-bdc6-7f53732a3361</v>
+        <v>65a44019-3d62-4701-9b04-03bd30cba68d</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D3" t="str">
-        <v>3ca3e100-c368-43ff-a72b-9575ae13adf2</v>
+        <v>b9037295-b281-4339-9c92-58351d8b0574</v>
       </c>
       <c r="E3" t="str">
-        <v>&lt;h2&gt;St. Regis Vommuli Transfer&lt;/h2&gt;&lt;p&gt;Standard seaplane transfer contract. Flight time approximately &lt;strong&gt;45 minutes&lt;/strong&gt; from Velana International Airport.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Butler service coordination for arrivals&lt;/li&gt;&lt;li&gt;Weather delay protocol: speedboat backup if needed&lt;/li&gt;&lt;/ul&gt;</v>
+        <v>&lt;h2&gt;St. Regis Vommuli Transfer&lt;/h2&gt;&lt;p&gt;2-year seaplane transfer contract for St. Regis Maldives Vommuli. Flight time approximately &lt;strong&gt;45 minutes&lt;/strong&gt; from Velana International Airport.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Butler service coordination for VIP arrivals&lt;/li&gt;&lt;li&gt;Weather delay protocol: speedboat backup arrangement with partner operator&lt;/li&gt;&lt;li&gt;30 guaranteed seats daily during peak season&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Long-term contract secured through Feb 2027.&lt;/p&gt;</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>54be72c6-ef17-4afb-9ea5-0654fffae00d</v>
+        <v>fc863e60-ac03-42d8-8c48-402f9bcde026</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D4" t="str">
-        <v>8460e4e7-8321-4274-b1fa-e7828dd88619</v>
+        <v>a88b36f6-364e-4b60-974f-222c0081fc60</v>
       </c>
       <c r="E4" t="str">
-        <v>&lt;h2&gt;Soneva Fushi Charter Agreement&lt;/h2&gt;&lt;p&gt;Dedicated charter service for Soneva Fushi resort. &lt;strong&gt;Aircraft:&lt;/strong&gt; DHC-6 Twin Otter (19 seats).&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Aircraft branded with Soneva livery&lt;/li&gt;&lt;li&gt;Custom in-flight refreshments provided by resort&lt;/li&gt;&lt;li&gt;Flexible scheduling based on guest arrivals&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;em&gt;Renewal discussions to begin Q1 2026.&lt;/em&gt;&lt;/p&gt;</v>
+        <v>&lt;h2&gt;Soneva Fushi - Triple Contract&lt;/h2&gt;&lt;p&gt;Comprehensive 3-contract arrangement covering Charter, Transfer, and Signed Charter services for Soneva Fushi. &lt;strong&gt;Aircraft:&lt;/strong&gt; DHC-6 Twin Otter (19 seats).&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Charter (CTR-003-001): Dedicated aircraft with Soneva livery, custom in-flight refreshments&lt;/li&gt;&lt;li&gt;Transfer (CTR-003-002): Standard scheduled seaplane service for regular guests&lt;/li&gt;&lt;li&gt;Signed Charter (CTR-003-003): Premium VIP service with luxury cabin configuration&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Soneva Group is TMA's largest charter partner in Baa Atoll. &lt;em&gt;Contract value exceeds $2M annually.&lt;/em&gt;&lt;/p&gt;</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>1716b1f7-381d-4c20-84e7-8f916da871e9</v>
+        <v>7255990f-9063-4a16-95f9-066722fbf336</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D5" t="str">
-        <v>c46c84c4-734a-4a60-b97e-9b98b863dab9</v>
+        <v>9a4b1770-6a3e-42c5-b683-6bae0cafa620</v>
       </c>
       <c r="E5" t="str">
-        <v>&lt;h2&gt;Cheval Blanc - Expired Contract&lt;/h2&gt;&lt;p&gt;This contract expired on 31 Dec 2024. &lt;strong&gt;Status:&lt;/strong&gt; Pending renewal negotiations.&lt;/p&gt;&lt;p&gt;LVMH team to provide updated terms by March 2025.&lt;/p&gt;</v>
+        <v>&lt;h2&gt;Cheval Blanc - Expired Contract&lt;/h2&gt;&lt;p&gt;This signed charter contract expired on 31 Dec 2024. &lt;strong&gt;Status:&lt;/strong&gt; Pending renewal negotiations.&lt;/p&gt;&lt;p&gt;LVMH team evaluating competitive bids. TMA submitted revised proposal Jan 2025. Expected decision Q2 2025.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Note:&lt;/strong&gt; Interim transfer service provided on ad-hoc basis at published rates.&lt;/p&gt;</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>bd5c3b0b-0fa2-4eb7-a8d8-43855ca247a5</v>
+        <v>5cf3c019-3b33-4e3c-ac82-00bc4ef4eb59</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D6" t="str">
-        <v>18074a3c-28d1-4af9-bfcb-729b210cc637</v>
+        <v>8003b4e4-5d86-4a0e-90e2-d92850a7b277</v>
       </c>
       <c r="E6" t="str">
-        <v>&lt;h2&gt;Patina Maldives Transfer&lt;/h2&gt;&lt;p&gt;Transfer service for Patina Maldives, Fari Islands. Located in &lt;strong&gt;North Malé Atoll&lt;/strong&gt; - shorter flight time (~20 min).&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Combined service with Ritz-Carlton Fari where possible&lt;/li&gt;&lt;li&gt;Shared lounge facilities at VIA&lt;/li&gt;&lt;/ul&gt;</v>
+        <v>&lt;h2&gt;Patina Maldives - Transfer &amp; Charter&lt;/h2&gt;&lt;p&gt;Dual contract for Patina Maldives, Fari Islands. Located in &lt;strong&gt;North Malé Atoll&lt;/strong&gt; - shorter flight time (~20 min seaplane).&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Transfer (CTR-005-001): 2-year contract, shared service coordination with Ritz-Carlton Fari&lt;/li&gt;&lt;li&gt;Charter (CTR-005-002): Dedicated service for Marriott Bonvoy Platinum events&lt;/li&gt;&lt;li&gt;Shared lounge facilities at Velana International Airport&lt;/li&gt;&lt;/ul&gt;</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>a259cf0c-5bb1-4028-acd6-4d6ad35bde54</v>
+        <v>8a58fe38-f1e4-420a-b172-0836da6fa153</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D7" t="str">
-        <v>56914a2b-bd6a-418c-8e32-4b7bf224404c</v>
+        <v>6d461192-db6a-452f-b9da-1b11c9a51892</v>
       </c>
       <c r="E7" t="str">
-        <v>&lt;h2&gt;Four Seasons Landaa Giraavaru&lt;/h2&gt;&lt;p&gt;Premium seaplane service to Baa Atoll. &lt;strong&gt;Flight time:&lt;/strong&gt; ~35 minutes.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;UNESCO Biosphere Reserve location - special approach required&lt;/li&gt;&lt;li&gt;Marine biology equipment transport arrangements in place&lt;/li&gt;&lt;li&gt;Peak season (Nov-Apr): 50 guaranteed seats daily&lt;/li&gt;&lt;li&gt;Aerial photography package available as add-on&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Account manager: Sarah Chen, FS Regional Office&lt;/p&gt;</v>
+        <v>&lt;h2&gt;Four Seasons Landaa Giraavaru - Premium Triple&lt;/h2&gt;&lt;p&gt;TMA's most comprehensive contract: 3-year transfer + 2-year charter + 1-year signed charter for FS Landaa Giraavaru in Baa Atoll. &lt;strong&gt;Flight time:&lt;/strong&gt; ~35 minutes.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;UNESCO Biosphere Reserve location - special low-altitude approach required&lt;/li&gt;&lt;li&gt;Marine biology equipment transport arrangements in place&lt;/li&gt;&lt;li&gt;Peak season (Nov-Apr): 50 guaranteed seats daily&lt;/li&gt;&lt;li&gt;Aerial photography and sunset scenic flight packages available&lt;/li&gt;&lt;li&gt;Signed charter with VIP cabin configuration for ultra-high-net-worth guests&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Account manager: Sarah Chen, FS Regional Office. &lt;em&gt;Highest-value contract in portfolio at ~$3.5M/year.&lt;/em&gt;&lt;/p&gt;</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>c86a3ec7-8ff0-484b-b995-bbe068edbdba</v>
+        <v>6e248b58-a663-43e8-9596-dbf7092e0b3a</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D8" t="str">
-        <v>972c7ed7-e881-472b-b5b8-3308c95bbfe7</v>
+        <v>751a7f5c-6eb1-4059-a3f3-28923fbed286</v>
       </c>
       <c r="E8" t="str">
-        <v>&lt;h2&gt;Four Seasons Kuda Huraa - Speedboat&lt;/h2&gt;&lt;p&gt;Speedboat transfer service. &lt;strong&gt;Duration:&lt;/strong&gt; ~25 minutes from Velana Airport.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Closest Four Seasons property to airport&lt;/li&gt;&lt;li&gt;Extended operating hours until 22:00&lt;/li&gt;&lt;li&gt;High-frequency service during peak hours&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;em&gt;Contract expiring soon - renewal terms under discussion.&lt;/em&gt;&lt;/p&gt;</v>
+        <v>&lt;h2&gt;Four Seasons Kuda Huraa - Dual Transfer&lt;/h2&gt;&lt;p&gt;Combined speedboat and seaplane transfer for the closest Four Seasons property to Male airport.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Speedboat (CTR-007-001): 25-minute journey, extended hours until 22:00, every 30 minutes at peak&lt;/li&gt;&lt;li&gt;Seaplane (CTR-007-002): Alternative for guests preferring aerial arrival, ~15 min flight&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;em&gt;Both contracts expiring March 2026 - renewal terms under active discussion. FS requesting 10% rate reduction.&lt;/em&gt;&lt;/p&gt;</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>f66b5780-e71e-432e-b5ef-f7f404b29fa8</v>
+        <v>796c105d-7af7-4d35-a74b-505ae48e1342</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D9" t="str">
-        <v>f99c4af2-4b31-460a-ba00-3d940a1db42e</v>
+        <v>b015f249-d107-4b91-a15a-f882a23c73a6</v>
       </c>
       <c r="E9" t="str">
-        <v>&lt;h2&gt;Anantara Kihavah Charter&lt;/h2&gt;&lt;p&gt;Charter agreement for Anantara Kihavah Villas, Baa Atoll. &lt;strong&gt;Includes:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Dedicated DHC-6 Twin Otter aircraft&lt;/li&gt;&lt;li&gt;Overwater observatory transfers for astronomy programme&lt;/li&gt;&lt;li&gt;Dive equipment transport arrangements&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Minor Hotels regional team oversees operations.&lt;/p&gt;</v>
+        <v>&lt;h2&gt;Anantara Kihavah - Charter &amp; Transfer&lt;/h2&gt;&lt;p&gt;2-year charter + 1-year transfer for Anantara Kihavah Villas, Baa Atoll. &lt;strong&gt;Includes:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Charter (CTR-008-001): Dedicated DHC-6 Twin Otter, overwater observatory transfers for astronomy programme&lt;/li&gt;&lt;li&gt;Transfer (CTR-008-002): Standard scheduled seaplane, dive equipment transport arrangements&lt;/li&gt;&lt;li&gt;Sunset scenic flight add-on popular with honeymooners&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Minor Hotels regional team oversees operations. 20% deposit required for charter bookings.&lt;/p&gt;</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>8f6d3b5f-7cf5-4a73-8725-d05d9fbdee7e</v>
+        <v>d271e3a0-8f93-432a-919c-759e0a5d4c83</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D10" t="str">
-        <v>0c9f09d7-c165-40f2-bf66-c025930d9a46</v>
+        <v>04bb15d6-9e8a-4631-b7e7-04dae158c4d2</v>
       </c>
       <c r="E10" t="str">
-        <v>&lt;h2&gt;Ritz-Carlton Fari Islands - Speedboat&lt;/h2&gt;&lt;p&gt;Speedboat transfer for The Ritz-Carlton Maldives, Fari Islands.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Shared speedboat service with Patina Maldives (same island cluster)&lt;/li&gt;&lt;li&gt;Luxury speedboat upgrade available at $250 per trip&lt;/li&gt;&lt;li&gt;20-minute journey from Velana Airport&lt;/li&gt;&lt;/ul&gt;</v>
+        <v>&lt;h2&gt;Ritz-Carlton Fari Islands - Speedboat&lt;/h2&gt;&lt;p&gt;Speedboat transfer for The Ritz-Carlton Maldives, Fari Islands.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Shared speedboat service coordination with Patina Maldives (same island cluster)&lt;/li&gt;&lt;li&gt;Luxury speedboat upgrade available at $250 per trip for private transfer&lt;/li&gt;&lt;li&gt;20-minute journey from Velana Airport&lt;/li&gt;&lt;li&gt;Fixed schedule every 45 minutes throughout the day&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Marriott centralized billing covers both RC Fari and Patina contracts.&lt;/p&gt;</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2ba9c211-fc87-4a03-af30-07670c637def</v>
+        <v>63d42901-b827-44e6-b4da-6b6f7ca0fc42</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D11" t="str">
-        <v>a475ecad-2589-4b10-b614-551819a228d4</v>
+        <v>daca0df5-90b1-426b-b6e8-4afd695e1cd0</v>
       </c>
       <c r="E11" t="str">
-        <v>&lt;h2&gt;Soneva Jani - Expired Charter&lt;/h2&gt;&lt;p&gt;This charter contract expired on 28 Feb 2025. &lt;strong&gt;Status:&lt;/strong&gt; Under renewal.&lt;/p&gt;&lt;p&gt;Soneva Group consolidating charter terms for both Fushi and Jani properties. New combined contract expected Q2 2025.&lt;/p&gt;</v>
+        <v>&lt;h2&gt;Soneva Jani - Expired Dual Contract&lt;/h2&gt;&lt;p&gt;Both charter and transfer contracts expired Feb 2025. &lt;strong&gt;Status:&lt;/strong&gt; Under renewal.&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Charter (CTR-010-001): Dedicated aircraft no longer assigned&lt;/li&gt;&lt;li&gt;Transfer (CTR-010-002): Ad-hoc service at published rates&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Soneva Group consolidating charter terms for both Fushi and Jani properties. New combined multi-property contract expected Q2 2025. Delay due to Soneva's expansion plans for third Maldives property.&lt;/p&gt;</v>
       </c>
     </row>
   </sheetData>
